--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105348</v>
+        <v>105355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 6756-2025 artfynd.xlsx
+++ b/artfynd/A 6756-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125796260</v>
       </c>
       <c r="B2" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125796259</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
